--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1547,6 +1547,452 @@
       <c r="AZ9" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136932566</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>136954151</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99273</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>564627</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6683389</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954151</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136954149</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>564631</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6683409</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954149</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>136954153</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>564627</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6683384</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954153</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>136954154</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99390</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>223621</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Skogsnattviol</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. latiflora</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Drejer) Løjtnant</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Holmgruvan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>564616</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6683408</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Hedemora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Garpenberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Fridh</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Vigge Ulfsson, Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136954154</t>
         </is>
       </c>
     </row>
@@ -1560,6 +2006,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99388</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99273</v>
+        <v>99279</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99396</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99279</v>
+        <v>99281</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99396</v>
+        <v>99397</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99281</v>
+        <v>99282</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99397</v>
+        <v>99403</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99282</v>
+        <v>99288</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99399</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99403</v>
+        <v>99407</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99288</v>
+        <v>99292</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99405</v>
+        <v>99409</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99407</v>
+        <v>99409</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99292</v>
+        <v>99294</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99409</v>
+        <v>99411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99294</v>
+        <v>99296</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99411</v>
+        <v>99413</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99411</v>
+        <v>99424</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99296</v>
+        <v>99309</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99413</v>
+        <v>99426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99424</v>
+        <v>99426</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99309</v>
+        <v>99311</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99426</v>
+        <v>99428</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99426</v>
+        <v>99429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99311</v>
+        <v>99314</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99428</v>
+        <v>99431</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99429</v>
+        <v>99439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99431</v>
+        <v>99441</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99439</v>
+        <v>99440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99441</v>
+        <v>99442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99440</v>
+        <v>99445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99442</v>
+        <v>99447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99445</v>
+        <v>99447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99447</v>
+        <v>99449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99447</v>
+        <v>99453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99449</v>
+        <v>99455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99453</v>
+        <v>99465</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99455</v>
+        <v>99467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99465</v>
+        <v>99466</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99467</v>
+        <v>99468</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99466</v>
+        <v>99469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99468</v>
+        <v>99471</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99469</v>
+        <v>99470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99354</v>
+        <v>99355</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99471</v>
+        <v>99472</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 34932-2024 artfynd.xlsx
+++ b/artfynd/A 34932-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136932567</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136932568</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136932571</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136932574</v>
       </c>
       <c r="B5" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136932569</v>
       </c>
       <c r="B6" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>136932570</v>
       </c>
       <c r="B7" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>136932573</v>
       </c>
       <c r="B8" t="n">
-        <v>99470</v>
+        <v>99473</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>136932566</v>
       </c>
       <c r="B9" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136954151</v>
       </c>
       <c r="B10" t="n">
-        <v>99355</v>
+        <v>99358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136954149</v>
       </c>
       <c r="B11" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>136954153</v>
       </c>
       <c r="B12" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>136954154</v>
       </c>
       <c r="B13" t="n">
-        <v>99472</v>
+        <v>99475</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
